--- a/research/alameda/deliverables/Elan_Banks_near_Alameda_v1.xlsx
+++ b/research/alameda/deliverables/Elan_Banks_near_Alameda_v1.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>Largest institution by deposits in the set</t>
+          <t>Largest institution by deposits in the set | MIXED PROGRAM (corrected 2026-07-26): the One Card (corporate/business) is Elan per East West's own page — "The creditor and issuer of the East West Bank One Card is Elan Financial Services, pursuant to a license from Visa U.S.A." BUT East West SELF-ISSUES its Secured Visa Classic (consumer; Elan not named) and books $4,631K of credit-card loans on its own balance sheet (FDIC call report 2026-03-31, CERT 31628). Do NOT label the bank flatly "Elan".</t>
         </is>
       </c>
     </row>
